--- a/translations/welsh-translations/xlsx/06-producer-certificate-start.xlsx
+++ b/translations/welsh-translations/xlsx/06-producer-certificate-start.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="57">
   <si>
     <t>Translator notes</t>
   </si>
@@ -19,6 +19,9 @@
     <t>Translations with syntax such as {{year}} should be preserved in the translated text, as it's a placeholder for a dynamic value</t>
   </si>
   <si>
+    <t>compliance.regulators.*.the are definite articles used before regulator names (for example 'the Environment Agency'). Wales has an empty article. Content may also supply a separate regulator-names brief.</t>
+  </si>
+  <si>
     <t>Reusable content rendered on this page is translated in: 00-shared-layout.xlsx.</t>
   </si>
   <si>
@@ -55,40 +58,49 @@
     <t/>
   </si>
   <si>
+    <t>https://www.figma.com/design/eG3Z7k6gmh9ZCtooRy0iBz/Certificate-Statement-of-Certification?node-id=4297-33233&amp;t=i61f1BsSBR1bSqaq-4</t>
+  </si>
+  <si>
+    <t>compliance.components.about.description1</t>
+  </si>
+  <si>
+    <t>Your certificate of compliance tells {{regulatorName}} whether you have met your recycling obligations for {{year}}.</t>
+  </si>
+  <si>
     <t>compliance.components.about.mustIntro</t>
   </si>
   <si>
     <t>You must:</t>
   </si>
   <si>
+    <t>compliance.components.about.mustBullet1</t>
+  </si>
+  <si>
+    <t>be an approved or delegated person to submit the certificate of compliance</t>
+  </si>
+  <si>
+    <t>compliance.components.about.mustBullet2</t>
+  </si>
+  <si>
+    <t>submit the certificate even if you have not met your recycling obligations</t>
+  </si>
+  <si>
+    <t>compliance.components.about.mustBullet3</t>
+  </si>
+  <si>
+    <t>submit on or before 31 January every year</t>
+  </si>
+  <si>
     <t>compliance.components.about.warning</t>
   </si>
   <si>
     <t>You may face enforcement action if you miss the deadline.</t>
   </si>
   <si>
-    <t>compliance.components.about.description1</t>
-  </si>
-  <si>
-    <t>Your certificate of compliance tells the {{regulatorName}} whether you have met your recycling obligations for {{year}}.</t>
-  </si>
-  <si>
-    <t>compliance.components.about.mustBullet1</t>
-  </si>
-  <si>
-    <t>be an approved or delegated person to submit the certificate of compliance</t>
-  </si>
-  <si>
-    <t>compliance.components.about.mustBullet2</t>
-  </si>
-  <si>
-    <t>submit the certificate even if you have not met your recycling obligations</t>
-  </si>
-  <si>
-    <t>compliance.components.about.mustBullet3</t>
-  </si>
-  <si>
-    <t>submit on or before 31 January every year</t>
+    <t>common.warningIconFallback</t>
+  </si>
+  <si>
+    <t>Warning</t>
   </si>
   <si>
     <t>compliance.components.about.howToTitle</t>
@@ -130,7 +142,7 @@
     <t>compliance.components.about.regulatorContact</t>
   </si>
   <si>
-    <t>If anything on your certificate is incorrect, contact the {{regulatorName}}:</t>
+    <t>If anything on your certificate is incorrect, contact {{regulatorName}}:</t>
   </si>
   <si>
     <t>compliance.components.about.finalStatus</t>
@@ -139,6 +151,12 @@
     <t>Your final certificate shows your recycling obligations status. To get a 'met' status, you must have met all of your recycling obligations.</t>
   </si>
   <si>
+    <t>common.continue</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
     <t>compliance.components.about.alreadySubmittedLead</t>
   </si>
   <si>
@@ -149,6 +167,21 @@
   </si>
   <si>
     <t>View confirmation</t>
+  </si>
+  <si>
+    <t>compliance.regulators.GB-ENG.the</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>compliance.regulators.GB-SCT.the</t>
+  </si>
+  <si>
+    <t>compliance.regulators.GB-WLS.the</t>
+  </si>
+  <si>
+    <t>compliance.regulators.GB-NIR.the</t>
   </si>
 </sst>
 </file>
@@ -547,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -577,105 +610,92 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="4" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -683,19 +703,19 @@
         <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -703,19 +723,19 @@
         <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -723,19 +743,19 @@
         <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -743,19 +763,19 @@
         <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -763,19 +783,19 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -783,19 +803,19 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -803,19 +823,19 @@
         <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -823,19 +843,19 @@
         <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -843,19 +863,19 @@
         <v>36</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -863,39 +883,39 @@
         <v>38</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -903,48 +923,192 @@
         <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F22"/>
-  <mergeCells count="3">
+  <autoFilter ref="A6:F29"/>
+  <mergeCells count="4">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F7" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/translations/welsh-translations/xlsx/06-producer-certificate-start.xlsx
+++ b/translations/welsh-translations/xlsx/06-producer-certificate-start.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F88371-999F-4DB9-A29B-85C0BC734720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
+    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
   <si>
     <t>Translator notes</t>
   </si>
@@ -19,9 +23,6 @@
     <t>Translations with syntax such as {{year}} should be preserved in the translated text, as it's a placeholder for a dynamic value</t>
   </si>
   <si>
-    <t>compliance.regulators.*.the are definite articles used before regulator names (for example 'the Environment Agency'). Wales has an empty article. Content may also supply a separate regulator-names brief.</t>
-  </si>
-  <si>
     <t>Reusable content rendered on this page is translated in: 00-shared-layout.xlsx.</t>
   </si>
   <si>
@@ -40,9 +41,6 @@
     <t>Welsh</t>
   </si>
   <si>
-    <t>Figma link</t>
-  </si>
-  <si>
     <t>compliance.certificate.heading</t>
   </si>
   <si>
@@ -182,27 +180,101 @@
   </si>
   <si>
     <t>compliance.regulators.GB-NIR.the</t>
+  </si>
+  <si>
+    <t>Figma link for all content on this page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the Figma file for the full page content. Text that is repeated within the service may be translated in another file and omitted here. </t>
+  </si>
+  <si>
+    <t>Compliance.regulators.*.the are definite articles used before regulator names (for example 'the Environment Agency'). Wales has an empty article. Content may also supply a separate regulator-names brief.</t>
+  </si>
+  <si>
+    <t>Rhaid i chi:</t>
+  </si>
+  <si>
+    <t>bod yn berson cymeradwy neu ddirprwyedig i gyflwyno’r dystysgrif cydymffurfio</t>
+  </si>
+  <si>
+    <t>cyflwyno ar 31 Ionawr neu cyn hynny bob blwyddyn</t>
+  </si>
+  <si>
+    <t>Gallwch wynebu camau gorfodi os byddwch yn methu’r dyddiad cau.</t>
+  </si>
+  <si>
+    <t>Rhybudd</t>
+  </si>
+  <si>
+    <t>Cyn cyflwyno, rhaid i chi wneud y canlynol:</t>
+  </si>
+  <si>
+    <t>gwirio manylion eich sefydliad</t>
+  </si>
+  <si>
+    <t>gwirio eich rhwymedigaethau ailgylchu</t>
+  </si>
+  <si>
+    <t>Os oes unrhyw beth anghywir ar eich tystysgrif, cysylltwch â {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>Mae eich tystysgrif derfynol yn dangos statws eich rhwymedigaethau ailgylchu. I gael statws ‘cyflawnwyd’ rhaid i chi fod wedi cyflawni eich holl rwymedigaethau ailgylchu.</t>
+  </si>
+  <si>
+    <t>Bwrw ymlaen</t>
+  </si>
+  <si>
+    <t>Rydych eisoes wedi cyflwyno eich tystysgrif cydymffurfio ar gyfer {{year}}.</t>
+  </si>
+  <si>
+    <t>Gweld y cadarnhad</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Gwybodaeth am eich tystysgrif cydymffurfio ar gyfer {{year}}</t>
+  </si>
+  <si>
+    <t>Mae eich tystysgrif cydymffurfio yn rhoi gwybod i {{regulatorName}} a ydych chi wedi cyflawni eich rhwymedigaethau ailgylchu ar gyfer {{year}}.</t>
+  </si>
+  <si>
+    <t>cyflwyno’r dystysgrif hyd yn oed os nad ydych wedi cyflawni eich rhwymedigaethau ailgylchu</t>
+  </si>
+  <si>
+    <t>Sut mae cyflwyno eich tystysgrif</t>
+  </si>
+  <si>
+    <t>Ar y sgrin nesaf gallwch wirio a chyflwyno eich tystysgrif cydymffurfio ar gyfer {{year}}.</t>
+  </si>
+  <si>
+    <t>rhoi eich enw llawn o dan y datganiad cyfreithiol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -230,15 +302,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -579,9 +657,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -589,527 +667,534 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="1" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="1" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F7" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="E9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="E10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="E11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="E12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="E13" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="E14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="E15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="E16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="E17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="E18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="E19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="E20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="E21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="E22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="E23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="E24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="E25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="E26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="E27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>14</v>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:F29"/>
-  <mergeCells count="4">
+  <autoFilter ref="A7:F30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="5">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1"/>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>